--- a/output/full_scan/batch_seq8_2026-09-09.xlsx
+++ b/output/full_scan/batch_seq8_2026-09-09.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6922</v>
+        <v>6933</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>661.2832911147791</v>
+        <v>663.097097868013</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>196.5</v>
+        <v>338</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>48.1420964589689</v>
+        <v>77.95555408380544</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.98616843503113</v>
+        <v>46.57945612189177</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3765970392981324</v>
+        <v>0.6053263505645433</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.696517277907296</v>
+        <v>8.21653198800518</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7788</v>
+        <v>6922</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>648.9579864394354</v>
+        <v>661.2832911147791</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>320.5</v>
+        <v>196.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.73931397569498</v>
+        <v>48.1420964589689</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31.49110660453566</v>
+        <v>23.98616843503113</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.087813411709159</v>
+        <v>0.3765970392981324</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.900060555261188</v>
+        <v>-1.696517277907296</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6913</v>
+        <v>7788</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>613.5947233995812</v>
+        <v>648.9579864394354</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>131</v>
+        <v>320.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40.0477114786053</v>
+        <v>60.73931397569498</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.13021646046596</v>
+        <v>31.49110660453566</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4621659539033356</v>
+        <v>1.087813411709159</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-3.148770751418563</v>
+        <v>0.900060555261188</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7631</v>
+        <v>6913</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>601.2344852597051</v>
+        <v>613.5947233995812</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.20598618735504</v>
+        <v>40.0477114786053</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.65877582907471</v>
+        <v>24.13021646046596</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.202794949394585</v>
+        <v>0.4621659539033356</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-0.3770747354177934</v>
+        <v>-3.148770751418563</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6916</v>
+        <v>7631</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>599.7472769672764</v>
+        <v>601.2344852597051</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>19.05</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.69905920665583</v>
+        <v>51.20598618735504</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12.8435547820852</v>
+        <v>23.65877582907471</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.135698922795871</v>
+        <v>0.202794949394585</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.07672059970900789</v>
+        <v>-0.3770747354177934</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6870</v>
+        <v>6916</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>589.5467795774251</v>
+        <v>599.7472769672764</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>289</v>
+        <v>19.05</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.167517159893</v>
+        <v>55.69905920665583</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.29038570580735</v>
+        <v>12.8435547820852</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.476352086881908</v>
+        <v>1.135698922795871</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>3.824530349401751</v>
+        <v>0.07672059970900789</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6918</v>
+        <v>6870</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>583.120928376886</v>
+        <v>589.5467795774251</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>289</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>60.67521003346869</v>
+        <v>59.167517159893</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>43.5148160134745</v>
+        <v>22.29038570580735</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.645906096903495</v>
+        <v>1.476352086881908</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.1147873569912936</v>
+        <v>3.824530349401751</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6887</v>
+        <v>6918</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>542.4512116038474</v>
+        <v>583.120928376886</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.7750003299382</v>
+        <v>60.67521003346869</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.56463711325586</v>
+        <v>43.5148160134745</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5179401520154345</v>
+        <v>0.645906096903495</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.030670776343054</v>
+        <v>0.1147873569912936</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6885</v>
+        <v>6887</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>521.3637330548701</v>
+        <v>542.4512116038474</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>26.65</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>76.45452818156633</v>
+        <v>53.7750003299382</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46.55669227493869</v>
+        <v>28.56463711325586</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.236373305487009</v>
+        <v>0.5179401520154345</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.4565273506847331</v>
+        <v>0.030670776343054</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7610</v>
+        <v>6885</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>521.0490568330985</v>
+        <v>521.3637330548701</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2030</v>
+        <v>26.65</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.27311487012771</v>
+        <v>76.45452818156633</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.58530522207709</v>
+        <v>46.55669227493869</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.711549415687319</v>
+        <v>1.236373305487009</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>61.01965065959001</v>
+        <v>0.4565273506847331</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7821</v>
+        <v>7610</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>515.5150204020182</v>
+        <v>521.0490568330985</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>40</v>
+        <v>2030</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.64771176418166</v>
+        <v>61.27311487012771</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12.92154114718008</v>
+        <v>16.58530522207709</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.127020934088671</v>
+        <v>1.711549415687319</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1664348873738906</v>
+        <v>61.01965065959001</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6907</v>
+        <v>7821</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>515.3408999972323</v>
+        <v>515.5150204020182</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>195.5</v>
+        <v>40</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.62798176841108</v>
+        <v>53.64771176418166</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16.3079181664347</v>
+        <v>12.92154114718008</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.487204788922789</v>
+        <v>1.127020934088671</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.361052815168761</v>
+        <v>0.1664348873738906</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6937</v>
+        <v>6907</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>506.4191316418858</v>
+        <v>515.3408999972323</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>291</v>
+        <v>195.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.92664315558125</v>
+        <v>54.62798176841108</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.22922419506165</v>
+        <v>16.3079181664347</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6783204615019807</v>
+        <v>1.487204788922789</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.210606343353142</v>
+        <v>1.361052815168761</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6949</v>
+        <v>6937</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>506</v>
+        <v>506.4191316418858</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>54.9</v>
+        <v>291</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>25.37256568661647</v>
+        <v>56.92664315558125</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>40.28214240679264</v>
+        <v>14.22922419506165</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8.331334001558657</v>
+        <v>0.6783204615019807</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-123.1128397409994</v>
+        <v>1.210606343353142</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6983</v>
+        <v>6949</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>501.4610502694957</v>
+        <v>506</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>351.5</v>
+        <v>54.9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.97382222456724</v>
+        <v>25.37256568661647</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.46121040532651</v>
+        <v>40.28214240679264</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.270480623953611</v>
+        <v>8.331334001558657</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.863856895073054</v>
+        <v>-123.1128397409994</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7795</v>
+        <v>6983</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>498.8562929674517</v>
+        <v>501.4610502694957</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>548</v>
+        <v>351.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.03288103274019</v>
+        <v>59.97382222456724</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18.44605873466563</v>
+        <v>25.46121040532651</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.972224497431594</v>
+        <v>1.270480623953611</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-2.851884070115858</v>
+        <v>3.863856895073054</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6969</v>
+        <v>7795</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>495.2963717010141</v>
+        <v>498.8562929674517</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>34.5</v>
+        <v>548</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.03555923672337</v>
+        <v>55.03288103274019</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.75298305895661</v>
+        <v>18.44605873466563</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.148004872163128</v>
+        <v>0.972224497431594</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.1032313451624671</v>
+        <v>-2.851884070115858</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7732</v>
+        <v>6969</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>487.6472577936809</v>
+        <v>495.2963717010141</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>51.34331147307898</v>
+        <v>53.03555923672337</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5.819639229299831</v>
+        <v>22.75298305895661</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.266193197699026</v>
+        <v>2.148004872163128</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0070857698567817</v>
+        <v>-0.1032313451624671</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7734</v>
+        <v>7732</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>478.7246094392215</v>
+        <v>487.6472577936809</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2980</v>
+        <v>34.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.71863268345444</v>
+        <v>51.34331147307898</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.1968523139422</v>
+        <v>5.819639229299831</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7476325505124404</v>
+        <v>0.266193197699026</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>12.4826604056822</v>
+        <v>0.0070857698567817</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6924</v>
+        <v>7734</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>467.2181061830515</v>
+        <v>478.7246094392215</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>125.5</v>
+        <v>2980</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>62.26846722882787</v>
+        <v>49.71863268345444</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.06506018161821</v>
+        <v>14.1968523139422</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3218106183051468</v>
+        <v>0.7476325505124404</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.401500690216842</v>
+        <v>12.4826604056822</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6952</v>
+        <v>6924</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>457.4232974608693</v>
+        <v>467.2181061830515</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>38.9</v>
+        <v>125.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.72417534364129</v>
+        <v>62.26846722882787</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.73553013056191</v>
+        <v>26.06506018161821</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3965487734120309</v>
+        <v>0.3218106183051468</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2643019529423478</v>
+        <v>1.401500690216842</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6895</v>
+        <v>6952</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>457.2860555621223</v>
+        <v>457.4232974608693</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>154.5</v>
+        <v>38.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.83800026178692</v>
+        <v>52.72417534364129</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>32.48501163439814</v>
+        <v>17.73553013056191</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.1545680477762528</v>
+        <v>0.3965487734120309</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.010441277028739</v>
+        <v>0.2643019529423478</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7769</v>
+        <v>6895</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>444.9409702475189</v>
+        <v>457.2860555621223</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6720</v>
+        <v>154.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.73496178069417</v>
+        <v>61.83800026178692</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13.00637266036075</v>
+        <v>32.48501163439814</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.186657897988937</v>
+        <v>0.1545680477762528</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>68.22233213518913</v>
+        <v>1.010441277028739</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7842</v>
+        <v>7769</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>444.5320918034628</v>
+        <v>444.9409702475189</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>6720</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.90105554141649</v>
+        <v>56.73496178069417</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.14962912736064</v>
+        <v>13.00637266036075</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5771284078586635</v>
+        <v>1.186657897988937</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.5524068229136052</v>
+        <v>68.22233213518913</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6944</v>
+        <v>7842</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>439.5743552273623</v>
+        <v>444.5320918034628</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>715</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>43.03117823333075</v>
+        <v>53.90105554141649</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>24.41342063560779</v>
+        <v>17.14962912736064</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8885094437123406</v>
+        <v>0.5771284078586635</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>6.159887101675192</v>
+        <v>-0.5524068229136052</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7714</v>
+        <v>6944</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>434.1677914406242</v>
+        <v>439.5743552273623</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>158.5</v>
+        <v>715</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45.92023330259421</v>
+        <v>43.03117823333075</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.34126085453974</v>
+        <v>24.41342063560779</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2859203478790333</v>
+        <v>0.8885094437123406</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-2.280387562699691</v>
+        <v>6.159887101675192</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6936</v>
+        <v>7714</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>433.8543336552444</v>
+        <v>434.1677914406242</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>32.7</v>
+        <v>158.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>54.05705496035267</v>
+        <v>45.92023330259421</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>38.77330312277469</v>
+        <v>18.34126085453974</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.039749447144797</v>
+        <v>0.2859203478790333</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.025868814832116</v>
+        <v>-2.280387562699691</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6890</v>
+        <v>6936</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>431.6073031199927</v>
+        <v>433.8543336552444</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>157</v>
+        <v>32.7</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>38.06437723022125</v>
+        <v>54.05705496035267</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14.86206322832033</v>
+        <v>38.77330312277469</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.559311163192469</v>
+        <v>1.039749447144797</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0131643774759653</v>
+        <v>0.025868814832116</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8016</v>
+        <v>6890</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>427.4768584710757</v>
+        <v>431.6073031199927</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.00228916589435</v>
+        <v>38.06437723022125</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>9.886029411878472</v>
+        <v>14.86206322832033</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8540417006399748</v>
+        <v>1.559311163192469</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.363987316429304</v>
+        <v>0.0131643774759653</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6838</v>
+        <v>8016</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>427.3991896481066</v>
+        <v>427.4768584710757</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>23.95</v>
+        <v>284</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.25214515752165</v>
+        <v>44.00228916589435</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.36661889739449</v>
+        <v>9.886029411878472</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.9550772300857784</v>
+        <v>0.8540417006399748</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1606199512603016</v>
+        <v>-1.363987316429304</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7751</v>
+        <v>6838</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>426.1820186521909</v>
+        <v>427.3991896481066</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1610</v>
+        <v>23.95</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.72389049132675</v>
+        <v>55.25214515752165</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.77095980208177</v>
+        <v>21.36661889739449</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3407405110987193</v>
+        <v>0.9550772300857784</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-22.96159146233128</v>
+        <v>0.1606199512603016</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6903</v>
+        <v>7751</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>421.7684027485927</v>
+        <v>426.1820186521909</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>316</v>
+        <v>1610</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.25017339764444</v>
+        <v>52.72389049132675</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.09124877469347</v>
+        <v>14.77095980208177</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7150112638171342</v>
+        <v>0.3407405110987193</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.921058691662955</v>
+        <v>-22.96159146233128</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6994</v>
+        <v>6903</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>421.3980741900427</v>
+        <v>421.7684027485927</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>32.87269959626377</v>
+        <v>48.25017339764444</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>27.6484227291679</v>
+        <v>13.09124877469347</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.304944123870713</v>
+        <v>0.7150112638171342</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1568936819384501</v>
+        <v>1.921058691662955</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6906</v>
+        <v>6994</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>419.4991728599537</v>
+        <v>421.3980741900427</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>81.2</v>
+        <v>34</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.41858145474314</v>
+        <v>32.87269959626377</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>34.31247252554397</v>
+        <v>27.6484227291679</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6137330931820567</v>
+        <v>2.304944123870713</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.028630077357358</v>
+        <v>0.1568936819384501</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7712</v>
+        <v>6906</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>419.3723673156841</v>
+        <v>419.4991728599537</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>151</v>
+        <v>81.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.25472459838874</v>
+        <v>57.41858145474314</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.73882824543601</v>
+        <v>34.31247252554397</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.2792573903210829</v>
+        <v>0.6137330931820567</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.3185552019356068</v>
+        <v>1.028630077357358</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7721</v>
+        <v>7712</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>414.4991127959179</v>
+        <v>419.3723673156841</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>53.85467450464611</v>
+        <v>50.25472459838874</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14.10622743736467</v>
+        <v>19.73882824543601</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.539788980862922</v>
+        <v>0.2792573903210829</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2171162288296243</v>
+        <v>0.3185552019356068</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8024</v>
+        <v>7721</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>411.321561996401</v>
+        <v>414.4991127959179</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>13.15</v>
+        <v>63</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>42.81660251055594</v>
+        <v>53.85467450464611</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.68296712560611</v>
+        <v>14.10622743736467</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.587689719042805</v>
+        <v>1.539788980862922</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0454230746673028</v>
+        <v>0.2171162288296243</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7750</v>
+        <v>8024</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>411.1513330432427</v>
+        <v>411.321561996401</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2270</v>
+        <v>13.15</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.61804731156188</v>
+        <v>42.81660251055594</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11.10233725353546</v>
+        <v>13.68296712560611</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2692459794358028</v>
+        <v>1.587689719042805</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-13.47512478907828</v>
+        <v>0.0454230746673028</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7855</v>
+        <v>7750</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>406.6345659687581</v>
+        <v>411.1513330432427</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>42.15</v>
+        <v>2270</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>17.46928894676257</v>
+        <v>48.61804731156188</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>53.08310340875093</v>
+        <v>11.10233725353546</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3834451037512054</v>
+        <v>0.2692459794358028</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.7790154101698</v>
+        <v>-13.47512478907828</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6855</v>
+        <v>7855</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>398.862930679449</v>
+        <v>406.6345659687581</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>120</v>
+        <v>42.15</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.39471653443428</v>
+        <v>17.46928894676257</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9.212120522389412</v>
+        <v>53.08310340875093</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.96073289067436</v>
+        <v>0.3834451037512054</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>7.091013482785182</v>
+        <v>1.7790154101698</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8034</v>
+        <v>6855</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>395.8630438126182</v>
+        <v>398.862930679449</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>20.3</v>
+        <v>120</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>57.18785344543782</v>
+        <v>52.39471653443428</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>27.52304046948402</v>
+        <v>9.212120522389412</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7108843522089995</v>
+        <v>1.96073289067436</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.197727627401234</v>
+        <v>7.091013482785182</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6958</v>
+        <v>8034</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>391.8630334788229</v>
+        <v>395.8630438126182</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>17.45</v>
+        <v>20.3</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.71965368238554</v>
+        <v>57.18785344543782</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.4227213236887</v>
+        <v>27.52304046948402</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6903582181550935</v>
+        <v>0.7108843522089995</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0046953605181899</v>
+        <v>0.197727627401234</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7728</v>
+        <v>6958</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>388.2707403518838</v>
+        <v>391.8630334788229</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>627</v>
+        <v>17.45</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.11741417893418</v>
+        <v>47.71965368238554</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>18.22500743587192</v>
+        <v>15.4227213236887</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5110289974555311</v>
+        <v>0.6903582181550935</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>2.41083840189212</v>
+        <v>-0.0046953605181899</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6996</v>
+        <v>7728</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>387.8436248761993</v>
+        <v>388.2707403518838</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>170.5</v>
+        <v>627</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>38.45495667252287</v>
+        <v>52.11741417893418</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.52167756420787</v>
+        <v>18.22500743587192</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6383161290876173</v>
+        <v>0.5110289974555311</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.7210765945058195</v>
+        <v>2.41083840189212</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8039</v>
+        <v>6996</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>379.2256693823185</v>
+        <v>387.8436248761993</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>289.5</v>
+        <v>170.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.77657778483198</v>
+        <v>38.45495667252287</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>32.41522880519011</v>
+        <v>14.52167756420787</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8225669382318479</v>
+        <v>0.6383161290876173</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-5.457222667757542</v>
+        <v>-0.7210765945058195</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7765</v>
+        <v>8039</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>379.1871007956045</v>
+        <v>379.2256693823185</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>218.5</v>
+        <v>289.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>34.68408572866532</v>
+        <v>52.77657778483198</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21.49404867364307</v>
+        <v>32.41522880519011</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.529098776157901</v>
+        <v>0.8225669382318479</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.508197293922191</v>
+        <v>-5.457222667757542</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6894</v>
+        <v>7765</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>375.3143836086961</v>
+        <v>379.1871007956045</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>338</v>
+        <v>218.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.3542911899149</v>
+        <v>34.68408572866532</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.11578233475961</v>
+        <v>21.49404867364307</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.821022281520733</v>
+        <v>1.529098776157901</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3912688194245666</v>
+        <v>-0.508197293922191</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6928</v>
+        <v>6894</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>373.3597470610538</v>
+        <v>375.3143836086961</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>48.3</v>
+        <v>338</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.04164143440757</v>
+        <v>47.3542911899149</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.72070150968524</v>
+        <v>17.11578233475961</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2093106650992606</v>
+        <v>0.821022281520733</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1307371811337191</v>
+        <v>0.3912688194245666</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7402</v>
+        <v>6928</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>369.4048865183389</v>
+        <v>373.3597470610538</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>102</v>
+        <v>48.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.75381770145035</v>
+        <v>49.04164143440757</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.70531611430578</v>
+        <v>12.72070150968524</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.1431387270981179</v>
+        <v>0.2093106650992606</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.7971032276335981</v>
+        <v>0.1307371811337191</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6962</v>
+        <v>8021</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>367.5616122252786</v>
+        <v>373.096995663611</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>31.1</v>
+        <v>442.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.52712949238198</v>
+        <v>52.8147653456002</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.56708580244518</v>
+        <v>11.67251360473812</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.431954026363114</v>
+        <v>0.1884337982208671</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0816769145835794</v>
+        <v>3.854455961072985</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7768</v>
+        <v>7402</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>366.7379224340892</v>
+        <v>369.4048865183389</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>276.5</v>
+        <v>102</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45.15163836985192</v>
+        <v>42.75381770145035</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.30930128378108</v>
+        <v>16.70531611430578</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5552437739409135</v>
+        <v>0.1431387270981179</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1718554404020968</v>
+        <v>-0.7971032276335981</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7822</v>
+        <v>6962</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>365.5509089709344</v>
+        <v>367.5616122252786</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>902</v>
+        <v>31.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.0147516304006</v>
+        <v>43.52712949238198</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.7480558958322</v>
+        <v>13.56708580244518</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6879221827824892</v>
+        <v>0.431954026363114</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.3671699202219018</v>
+        <v>0.0816769145835794</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6861</v>
+        <v>7768</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>361.4802004026277</v>
+        <v>366.7379224340892</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>185.5</v>
+        <v>276.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>41.10015851534182</v>
+        <v>45.15163836985192</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.95736412422504</v>
+        <v>17.30930128378108</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.425929349129803</v>
+        <v>0.5552437739409135</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.965113270892859</v>
+        <v>-0.1718554404020968</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6934</v>
+        <v>7822</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>360.5447912800029</v>
+        <v>365.5509089709344</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>76.7</v>
+        <v>902</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.81955351717202</v>
+        <v>48.0147516304006</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.7823976765559</v>
+        <v>10.7480558958322</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.635970979741154</v>
+        <v>0.6879221827824892</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.418860261457933</v>
+        <v>-0.3671699202219018</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6957</v>
+        <v>6861</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>357.0330374455648</v>
+        <v>361.4802004026277</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>220.5</v>
+        <v>185.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.24718457176508</v>
+        <v>41.10015851534182</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.2102906938418</v>
+        <v>19.95736412422504</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.008628796412074</v>
+        <v>2.425929349129803</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.161046775789531</v>
+        <v>1.965113270892859</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6951</v>
+        <v>6934</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>353.7987452224536</v>
+        <v>360.5447912800029</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>70.8</v>
+        <v>76.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.20163717177402</v>
+        <v>56.81955351717202</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>25.09534391006823</v>
+        <v>16.7823976765559</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.416558674001105</v>
+        <v>0.635970979741154</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0178825673231595</v>
+        <v>0.418860261457933</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7704</v>
+        <v>6957</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>345.5979692032083</v>
+        <v>357.0330374455648</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>61.1</v>
+        <v>220.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.61984521869439</v>
+        <v>52.24718457176508</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.8767467903453</v>
+        <v>12.2102906938418</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.611438383529272</v>
+        <v>1.008628796412074</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.4090697081208942</v>
+        <v>-0.161046775789531</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6919</v>
+        <v>6951</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>343.8094963192107</v>
+        <v>353.7987452224536</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>30.63703847718197</v>
+        <v>38.20163717177402</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25.53971827442743</v>
+        <v>25.09534391006823</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4510120922115082</v>
+        <v>2.416558674001105</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-2.230325909688174</v>
+        <v>0.0178825673231595</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7689</v>
+        <v>7704</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>335.3929493465604</v>
+        <v>345.5979692032083</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>163.5</v>
+        <v>61.1</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>30.08945795979085</v>
+        <v>49.61984521869439</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22.93183835358693</v>
+        <v>14.8767467903453</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5865014473128805</v>
+        <v>1.611438383529272</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.424611171182554</v>
+        <v>-0.4090697081208942</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8040</v>
+        <v>6919</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>334.8367447402555</v>
+        <v>343.8094963192107</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>79.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.70985817658485</v>
+        <v>30.63703847718197</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.3147666199633</v>
+        <v>25.53971827442743</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.336803925318093</v>
+        <v>0.4510120922115082</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.352193572555724</v>
+        <v>-2.230325909688174</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6971</v>
+        <v>7689</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>333.739846246039</v>
+        <v>335.3929493465604</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>25</v>
+        <v>163.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>34.1656767587196</v>
+        <v>30.08945795979085</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>17.80592343820659</v>
+        <v>22.93183835358693</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.569559708696938</v>
+        <v>0.5865014473128805</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.008765396395774399</v>
+        <v>0.424611171182554</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6931</v>
+        <v>8040</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>333.5201314693874</v>
+        <v>334.8367447402555</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>40.3</v>
+        <v>79.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.52429101600816</v>
+        <v>54.70985817658485</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.7636805229581</v>
+        <v>16.3147666199633</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.1763458931498329</v>
+        <v>1.336803925318093</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.1903743879584458</v>
+        <v>1.352193572555724</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6902</v>
+        <v>6971</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>333.5066436758107</v>
+        <v>333.739846246039</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.17821976375553</v>
+        <v>34.1656767587196</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10.41852569616426</v>
+        <v>17.80592343820659</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.721792748021351</v>
+        <v>1.569559708696938</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0399045484076592</v>
+        <v>-0.008765396395774399</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8032</v>
+        <v>6931</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>332.8128121200439</v>
+        <v>333.5201314693874</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>35.2</v>
+        <v>40.3</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>38.57058595601209</v>
+        <v>45.52429101600816</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.13011747601506</v>
+        <v>23.7636805229581</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.582319452766552</v>
+        <v>0.1763458931498329</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0267005712255149</v>
+        <v>-0.1903743879584458</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7772</v>
+        <v>6902</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>331</v>
+        <v>333.5066436758107</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>77.26094493653225</v>
+        <v>53.17821976375553</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.48122380898869</v>
+        <v>10.41852569616426</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>10.85458082499692</v>
+        <v>0.721792748021351</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>5.595169277375264</v>
+        <v>-0.0399045484076592</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6997</v>
+        <v>8032</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>322.8424332650389</v>
+        <v>332.8128121200439</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>68</v>
+        <v>35.2</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.06910952735266</v>
+        <v>38.57058595601209</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7.950645106856252</v>
+        <v>20.13011747601506</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.421691457411455</v>
+        <v>1.582319452766552</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.085860326351403</v>
+        <v>0.0267005712255149</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7738</v>
+        <v>7772</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>320.1084376928628</v>
+        <v>331</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>41.73835401096687</v>
+        <v>77.26094493653225</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>31.80002998419037</v>
+        <v>26.48122380898869</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7854619979436105</v>
+        <v>10.85458082499692</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.3269059766850991</v>
+        <v>5.595169277375264</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6914</v>
+        <v>6997</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>319.8481348944059</v>
+        <v>322.8424332650389</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>21.34149362932337</v>
+        <v>52.06910952735266</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>37.95591085922548</v>
+        <v>7.950645106856252</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2380716403966826</v>
+        <v>1.421691457411455</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-1.203669889343045</v>
+        <v>0.085860326351403</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6908</v>
+        <v>7738</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>309.9184644603727</v>
+        <v>320.1084376928628</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>30.1</v>
+        <v>165</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>34.02033123556186</v>
+        <v>41.73835401096687</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>28.28724501367786</v>
+        <v>31.80002998419037</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.264841116674523</v>
+        <v>0.7854619979436105</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1411198549253807</v>
+        <v>-0.3269059766850991</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7805</v>
+        <v>6914</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>305.0398140981262</v>
+        <v>319.8481348944059</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>510</v>
+        <v>121</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>32.65501637707268</v>
+        <v>21.34149362932337</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>37.73093128945381</v>
+        <v>37.95591085922548</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.2974020143590994</v>
+        <v>0.2380716403966826</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-3.869752764521735</v>
+        <v>-1.203669889343045</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7780</v>
+        <v>6908</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>303.0030559452026</v>
+        <v>309.9184644603727</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>16.65</v>
+        <v>30.1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.91206787545407</v>
+        <v>34.02033123556186</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.21789402249777</v>
+        <v>28.28724501367786</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5143799438060436</v>
+        <v>1.264841116674523</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0005206821266828</v>
+        <v>0.1411198549253807</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6865</v>
+        <v>7805</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>298.7501452627612</v>
+        <v>305.0398140981262</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>25.8</v>
+        <v>510</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>53.24567050191777</v>
+        <v>32.65501637707268</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9.304791721009876</v>
+        <v>37.73093128945381</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.344687668372042</v>
+        <v>0.2974020143590994</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.3999068060784625</v>
+        <v>-3.869752764521735</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6967</v>
+        <v>7780</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>297.6238211666084</v>
+        <v>303.0030559452026</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>66</v>
+        <v>16.65</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>34.86987196430171</v>
+        <v>43.91206787545407</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10.87284106062206</v>
+        <v>15.21789402249777</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.662382116660845</v>
+        <v>0.5143799438060436</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.6109215623773099</v>
+        <v>-0.0005206821266828</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6921</v>
+        <v>6865</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>295.6196266369187</v>
+        <v>298.7501452627612</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>63.9</v>
+        <v>25.8</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.55353224734514</v>
+        <v>53.24567050191777</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20.94834025680582</v>
+        <v>9.304791721009876</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.1055087043512406</v>
+        <v>1.344687668372042</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.4380582148998207</v>
+        <v>0.3999068060784625</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6923</v>
+        <v>6967</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>285.4211112987712</v>
+        <v>297.6238211666084</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.28094176468836</v>
+        <v>34.86987196430171</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8.228716139286433</v>
+        <v>10.87284106062206</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8679214958158369</v>
+        <v>2.662382116660845</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0073382462624598</v>
+        <v>-0.6109215623773099</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7730</v>
+        <v>6921</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>284.8413554608333</v>
+        <v>295.6196266369187</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>175</v>
+        <v>63.9</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.27107220777019</v>
+        <v>44.55353224734514</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.13802729701872</v>
+        <v>20.94834025680582</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2126916468942354</v>
+        <v>0.1055087043512406</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1462548052645993</v>
+        <v>-0.4380582148998207</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7770</v>
+        <v>6923</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>282.6394904634251</v>
+        <v>285.4211112987712</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>37</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.44428315812741</v>
+        <v>50.28094176468836</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>5.661028962557674</v>
+        <v>8.228716139286433</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3.449453223433007</v>
+        <v>0.8679214958158369</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0750846239926789</v>
+        <v>0.0073382462624598</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7749</v>
+        <v>7730</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>278.4470967579825</v>
+        <v>284.8413554608333</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>355.5</v>
+        <v>175</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.33888847171199</v>
+        <v>51.27107220777019</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.37028562763602</v>
+        <v>19.13802729701872</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8737711587231969</v>
+        <v>0.2126916468942354</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2003647644829795</v>
+        <v>0.1462548052645993</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8028</v>
+        <v>7770</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>267.7992968429469</v>
+        <v>282.6394904634251</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>236</v>
+        <v>37</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.09829254581155</v>
+        <v>51.44428315812741</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.96685205479283</v>
+        <v>5.661028962557674</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5480227325974545</v>
+        <v>3.449453223433007</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6758904510771764</v>
+        <v>-0.0750846239926789</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7747</v>
+        <v>7749</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>262.3410359172954</v>
+        <v>278.4470967579825</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>112</v>
+        <v>355.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>51.73330007096774</v>
+        <v>46.33888847171199</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>9.097497192467358</v>
+        <v>15.37028562763602</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.0754871642013487</v>
+        <v>0.8737711587231969</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-3.703501125988878</v>
+        <v>0.2003647644829795</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6873</v>
+        <v>8028</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>257.1367396767304</v>
+        <v>267.7992968429469</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>68.8</v>
+        <v>236</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.78063712659879</v>
+        <v>41.09829254581155</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.93032116364486</v>
+        <v>19.96685205479283</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3836669293008879</v>
+        <v>0.5480227325974545</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.449979612437454</v>
+        <v>0.6758904510771764</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7799</v>
+        <v>7747</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>252.7249921755748</v>
+        <v>262.3410359172954</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>386.5</v>
+        <v>112</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>55.51846469356514</v>
+        <v>51.73330007096774</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.26410782882697</v>
+        <v>9.097497192467358</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.008089021286755</v>
+        <v>0.0754871642013487</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>3.44987394089314</v>
+        <v>-3.703501125988878</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6869</v>
+        <v>6873</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>244.7093566768534</v>
+        <v>257.1367396767304</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>64.2</v>
+        <v>68.8</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>41.15055350348475</v>
+        <v>38.78063712659879</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.57081098833438</v>
+        <v>22.93032116364486</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3876035327665976</v>
+        <v>0.3836669293008879</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2036150507536834</v>
+        <v>0.449979612437454</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7839</v>
+        <v>7799</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>241.9155323668737</v>
+        <v>252.7249921755748</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>43</v>
+        <v>386.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>34.35650982125863</v>
+        <v>55.51846469356514</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>39.34170144603264</v>
+        <v>16.26410782882697</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6246857050046696</v>
+        <v>1.008089021286755</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1000585647215843</v>
+        <v>3.44987394089314</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7827</v>
+        <v>6869</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>241.0368812226561</v>
+        <v>244.7093566768534</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>151.5</v>
+        <v>64.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.86972237464735</v>
+        <v>41.15055350348475</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>11.73453193465129</v>
+        <v>11.57081098833438</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6291058515710518</v>
+        <v>0.3876035327665976</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.8297982446082064</v>
+        <v>-0.2036150507536834</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6909</v>
+        <v>7839</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>240.0484036546703</v>
+        <v>241.9155323668737</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>40.05</v>
+        <v>43</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>43.34777609916841</v>
+        <v>34.35650982125863</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.06388641948656</v>
+        <v>39.34170144603264</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.040621926965157</v>
+        <v>0.6246857050046696</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1770824958206528</v>
+        <v>-0.1000585647215843</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8033</v>
+        <v>7827</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>240.0326865059385</v>
+        <v>241.0368812226561</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>174.5</v>
+        <v>151.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.59023972503056</v>
+        <v>43.86972237464735</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10.27331378422381</v>
+        <v>11.73453193465129</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1721099366332883</v>
+        <v>0.6291058515710518</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.514601041688858</v>
+        <v>-0.8297982446082064</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6863</v>
+        <v>6909</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>239.8457422767948</v>
+        <v>240.0484036546703</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>40.05</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>31.51379697714195</v>
+        <v>43.34777609916841</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.34824161491125</v>
+        <v>16.06388641948656</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6326936131396026</v>
+        <v>1.040621926965157</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.263207451942019</v>
+        <v>0.1770824958206528</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7818</v>
+        <v>8033</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>239.51083213797</v>
+        <v>240.0326865059385</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>60</v>
+        <v>174.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>30.13144161582319</v>
+        <v>44.59023972503056</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.43741060474609</v>
+        <v>10.27331378422381</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.237006450975468</v>
+        <v>0.1721099366332883</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0565305983060886</v>
+        <v>-1.514601041688858</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6955</v>
+        <v>6863</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>239.0465450213501</v>
+        <v>239.8457422767948</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>98.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.06247109684661</v>
+        <v>31.51379697714195</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7.473570625221361</v>
+        <v>17.34824161491125</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4224608690933666</v>
+        <v>0.6326936131396026</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.376857564938337</v>
+        <v>-1.263207451942019</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7823</v>
+        <v>7818</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>238.42562375274</v>
+        <v>239.51083213797</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.55719542540966</v>
+        <v>30.13144161582319</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>24.28637813918585</v>
+        <v>17.43741060474609</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4186499575132468</v>
+        <v>1.237006450975468</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3573083891385878</v>
+        <v>0.0565305983060886</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7547</v>
+        <v>6955</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>236.1311923997402</v>
+        <v>239.0465450213501</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>49.25</v>
+        <v>98.7</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>39.3115101468818</v>
+        <v>46.06247109684661</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.07883469312741</v>
+        <v>7.473570625221361</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.421511876364597</v>
+        <v>0.4224608690933666</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1432709617649951</v>
+        <v>-1.376857564938337</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6862</v>
+        <v>7823</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>234.029970153666</v>
+        <v>238.42562375274</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>136.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.73996849729042</v>
+        <v>35.55719542540966</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.71829822861172</v>
+        <v>24.28637813918585</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7570890391750332</v>
+        <v>0.4186499575132468</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.67316693540872</v>
+        <v>-0.3573083891385878</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6854</v>
+        <v>7547</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>233.6499568754845</v>
+        <v>236.1311923997402</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>49.25</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.98379788991564</v>
+        <v>39.3115101468818</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.38055773260143</v>
+        <v>10.07883469312741</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6682753078740036</v>
+        <v>1.421511876364597</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.5106674065308172</v>
+        <v>-0.1432709617649951</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7722</v>
+        <v>6862</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>228.7925117606435</v>
+        <v>234.029970153666</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>272</v>
+        <v>136.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.51828947212136</v>
+        <v>40.73996849729042</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.612101885903677</v>
+        <v>13.71829822861172</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5254437028307652</v>
+        <v>0.7570890391750332</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.503476443937211</v>
+        <v>0.67316693540872</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7786</v>
+        <v>6854</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>227.7903108364451</v>
+        <v>233.6499568754845</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>115.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>34.94636249020225</v>
+        <v>42.98379788991564</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.73570331105989</v>
+        <v>17.38055773260143</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.484224935593582</v>
+        <v>0.6682753078740036</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.380387459970585</v>
+        <v>0.5106674065308172</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6965</v>
+        <v>7722</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>223.2406356927529</v>
+        <v>228.7925117606435</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>73.8</v>
+        <v>272</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.17302727211607</v>
+        <v>41.51828947212136</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>34.63042526273727</v>
+        <v>9.612101885903677</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.257266498377209</v>
+        <v>0.5254437028307652</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1183087706225521</v>
+        <v>-0.503476443937211</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7791</v>
+        <v>7786</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>219.6791605084404</v>
+        <v>227.7903108364451</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>55.6</v>
+        <v>115.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.33663305237965</v>
+        <v>34.94636249020225</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>33.39330039729688</v>
+        <v>18.73570331105989</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.148685073517221</v>
+        <v>1.484224935593582</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1285299386995069</v>
+        <v>-0.380387459970585</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6877</v>
+        <v>6965</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>219.451661869384</v>
+        <v>223.2406356927529</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>117.5</v>
+        <v>73.8</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.78669153288591</v>
+        <v>41.17302727211607</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.91687325434073</v>
+        <v>34.63042526273727</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.039641214180377</v>
+        <v>1.257266498377209</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.6001066983377017</v>
+        <v>0.1183087706225521</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7740</v>
+        <v>7791</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>219.2126186892813</v>
+        <v>219.6791605084404</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>133</v>
+        <v>55.6</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.86930997276842</v>
+        <v>37.33663305237965</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.94493797368834</v>
+        <v>33.39330039729688</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.070746979483403</v>
+        <v>1.148685073517221</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0002443801781639</v>
+        <v>0.1285299386995069</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6947</v>
+        <v>6877</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>214.175460554529</v>
+        <v>219.451661869384</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>70</v>
+        <v>117.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.31006144766911</v>
+        <v>48.78669153288591</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9.264144412090976</v>
+        <v>19.91687325434073</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6674293939051841</v>
+        <v>1.039641214180377</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2784885548269771</v>
+        <v>0.6001066983377017</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7820</v>
+        <v>7740</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>207.603849476772</v>
+        <v>219.2126186892813</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>117.5</v>
+        <v>133</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.23182863590377</v>
+        <v>43.86930997276842</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.75110722513458</v>
+        <v>12.94493797368834</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1144184299059036</v>
+        <v>1.070746979483403</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.6529009355387112</v>
+        <v>-0.0002443801781639</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8011</v>
+        <v>6947</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>195.938820027433</v>
+        <v>214.175460554529</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>15.55</v>
+        <v>70</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>37.19952860587491</v>
+        <v>42.31006144766911</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>24.70771374158632</v>
+        <v>9.264144412090976</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.849140401789389</v>
+        <v>0.6674293939051841</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0130965696979787</v>
+        <v>0.2784885548269771</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8038</v>
+        <v>7820</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>189.7784539179011</v>
+        <v>207.603849476772</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>30.8</v>
+        <v>117.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.67667919938327</v>
+        <v>50.23182863590377</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>21.03643688852754</v>
+        <v>15.75110722513458</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5965262065309109</v>
+        <v>0.1144184299059036</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1842014449508193</v>
+        <v>-0.6529009355387112</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7715</v>
+        <v>8011</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>178.8568128529211</v>
+        <v>195.938820027433</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>28.65</v>
+        <v>15.55</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>35.18445360809724</v>
+        <v>37.19952860587491</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>24.86708825783202</v>
+        <v>24.70771374158632</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2582745416504531</v>
+        <v>0.849140401789389</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1206028287673124</v>
+        <v>-0.0130965696979787</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7760</v>
+        <v>8038</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>178.4835733965833</v>
+        <v>189.7784539179011</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>42.53367967607992</v>
+        <v>40.67667919938327</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>7.925005353195596</v>
+        <v>21.03643688852754</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.1414894777699198</v>
+        <v>0.5965262065309109</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0294407447089941</v>
+        <v>0.1842014449508193</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6901</v>
+        <v>7715</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>172.9694915137429</v>
+        <v>178.8568128529211</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>15.1</v>
+        <v>28.65</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>39.06943194711337</v>
+        <v>35.18445360809724</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.13358394858437</v>
+        <v>24.86708825783202</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4794540971107585</v>
+        <v>0.2582745416504531</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1004752652763511</v>
+        <v>-0.1206028287673124</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7803</v>
+        <v>7760</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>166.9028312274831</v>
+        <v>178.4835733965833</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>19.3</v>
+        <v>32.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>43.37714357961429</v>
+        <v>42.53367967607992</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>10.10800230207002</v>
+        <v>7.925005353195596</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.781037568874602</v>
+        <v>0.1414894777699198</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0891359834443029</v>
+        <v>0.0294407447089941</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7705</v>
+        <v>6901</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>162.519615306249</v>
+        <v>172.9694915137429</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>29.95</v>
+        <v>15.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>42.47206710146199</v>
+        <v>39.06943194711337</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>14.48458010844643</v>
+        <v>14.13358394858437</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.1492240577993407</v>
+        <v>0.4794540971107585</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.07433025441621161</v>
+        <v>-0.1004752652763511</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6910</v>
+        <v>7803</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>155.2876561667473</v>
+        <v>166.9028312274831</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.91435718639456</v>
+        <v>43.37714357961429</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.36920825379882</v>
+        <v>10.10800230207002</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.4471198023561002</v>
+        <v>0.781037568874602</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0653414963486698</v>
+        <v>0.0891359834443029</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6925</v>
+        <v>7705</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>146.614046840337</v>
+        <v>162.519615306249</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>49.25</v>
+        <v>29.95</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>36.04443341954727</v>
+        <v>42.47206710146199</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>9.601330677203816</v>
+        <v>14.48458010844643</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.6849392194497761</v>
+        <v>0.1492240577993407</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.1140505304018009</v>
+        <v>-0.07433025441621161</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7736</v>
+        <v>6910</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>145.1161319778784</v>
+        <v>155.2876561667473</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.96492230470133</v>
+        <v>45.91435718639456</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.96271563709778</v>
+        <v>18.36920825379882</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4039321229814798</v>
+        <v>0.4471198023561002</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0676860807736345</v>
+        <v>0.0653414963486698</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6899</v>
+        <v>6925</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>130.6681857596408</v>
+        <v>146.614046840337</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>49.8</v>
+        <v>49.25</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.95882280042565</v>
+        <v>36.04443341954727</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.70099635707688</v>
+        <v>9.601330677203816</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3724515859378628</v>
+        <v>0.6849392194497761</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1169120371295043</v>
+        <v>0.1140505304018009</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6988</v>
+        <v>7736</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>95.0524539823906</v>
+        <v>145.1161319778784</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>12</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>50.54775328427069</v>
+        <v>50.96492230470133</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7.619160189185973</v>
+        <v>12.96271563709778</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.8959847085276411</v>
+        <v>0.4039321229814798</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,62 +7142,168 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0755902160397062</v>
+        <v>0.0676860807736345</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6899</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>創為精密</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>130.6681857596408</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>39.95882280042565</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>19.70099635707688</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.3724515859378628</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>0.1169120371295043</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>6988</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>威力暘-創</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>95.0524539823906</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>50.54775328427069</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>7.619160189185973</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.8959847085276411</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.0755902160397062</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>7753</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>星亞</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>54.61331055916168</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>36.65</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>41.19062628710069</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>8.259586707237347</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.2631675196025197</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>0.0718362514345465</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
